--- a/testcases/discount-optimization/discount-optimization-locations.xlsx
+++ b/testcases/discount-optimization/discount-optimization-locations.xlsx
@@ -1190,7 +1190,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-010</t>
+          <t>TC-DOP-OPT-007</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1373,7 +1373,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-011</t>
+          <t>TC-DOP-OPT-008</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1532,7 +1532,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-012</t>
+          <t>TC-DOP-OPT-009</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1690,7 +1690,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-013</t>
+          <t>TC-DOP-OPT-010</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1848,7 +1848,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-020</t>
+          <t>TC-DOP-OPT-011</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1959,7 +1959,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-021</t>
+          <t>TC-DOP-OPT-012</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2070,7 +2070,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-022</t>
+          <t>TC-DOP-OPT-013</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2158,7 +2158,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-030</t>
+          <t>TC-DOP-OPT-014</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2269,7 +2269,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-031</t>
+          <t>TC-DOP-OPT-015</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2380,7 +2380,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-032</t>
+          <t>TC-DOP-OPT-016</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2491,7 +2491,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-033</t>
+          <t>TC-DOP-OPT-017</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2579,7 +2579,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-040</t>
+          <t>TC-DOP-OPT-018</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2714,7 +2714,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-041</t>
+          <t>TC-DOP-OPT-019</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2825,7 +2825,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-050</t>
+          <t>TC-DOP-OPT-020</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2982,7 +2982,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-051</t>
+          <t>TC-DOP-OPT-021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3089,7 +3089,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-052</t>
+          <t>TC-DOP-OPT-022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3292,7 +3292,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-053</t>
+          <t>TC-DOP-OPT-023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3495,7 +3495,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-060</t>
+          <t>TC-DOP-OPT-024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-061</t>
+          <t>TC-DOP-OPT-025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3694,7 +3694,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-065</t>
+          <t>TC-DOP-OPT-026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3830,7 +3830,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-066</t>
+          <t>TC-DOP-OPT-027</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3966,7 +3966,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-067</t>
+          <t>TC-DOP-OPT-028</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4149,7 +4149,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-068</t>
+          <t>TC-DOP-OPT-029</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4332,7 +4332,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-070</t>
+          <t>TC-DOP-OPT-030</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4466,7 +4466,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-071</t>
+          <t>TC-DOP-OPT-031</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4555,7 +4555,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-072</t>
+          <t>TC-DOP-OPT-032</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4666,7 +4666,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-090</t>
+          <t>TC-DOP-OPT-033</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4823,7 +4823,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-091</t>
+          <t>TC-DOP-OPT-034</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5004,7 +5004,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-092</t>
+          <t>TC-DOP-OPT-035</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">

--- a/testcases/discount-optimization/discount-optimization-locations.xlsx
+++ b/testcases/discount-optimization/discount-optimization-locations.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M139"/>
+  <dimension ref="A1:M136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2982,12 +2982,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-021</t>
+          <t xml:space="preserve">TC-DOP-OPT-021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Save remains enabled after adding a location</t>
+          <t>Save round-trip — two dirty rows both persist after a single save</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3019,10 +3019,14 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Pending Automation</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr">
         <is>
           <t>Grid has completed its first paint. Save is disabled</t>
@@ -3030,12 +3034,12 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>1. Click the Add button.</t>
+          <t>1. Confirm Save is disabled on a fresh load.</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>The add affordance opens.</t>
+          <t>Save is disabled.</t>
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
@@ -3053,12 +3057,12 @@
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2. Complete the add form with a valid location and confirm (do not cancel).</t>
+          <t>2. Change the Allow Special Rate toggle on row A.</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>The new location appears in the grid as a pending row. Save is enabled.</t>
+          <t>Toggle state on row A changes. Save becomes enabled.</t>
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
@@ -3076,77 +3080,35 @@
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>3. Read the Save button state</t>
+          <t>3. Without saving, change the Allow Special Rate toggle on row B (a different row, not used by other tests).</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Save is enabled — the newly added row is a pending change.</t>
+          <t>Toggle state on row B changes. Save remains enabled.</t>
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>TC-DOP-OPT-022</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Save round-trip — two dirty rows both persist after a single save</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>discount-optimization</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>discount_optimization</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>Grid has completed its first paint. Save is disabled</t>
-        </is>
-      </c>
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>1. Confirm Save is disabled on a fresh load.</t>
+          <t>4. Click Save once.</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Save is disabled.</t>
+          <t>The save completes. Save becomes disabled.</t>
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
@@ -3164,12 +3126,12 @@
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2. Change the Allow Special Rate toggle on row A.</t>
+          <t>5. Reload the page and wait for the grid to complete its first paint.</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Toggle state on row A changes. Save becomes enabled.</t>
+          <t>The page reloads.</t>
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
@@ -3187,12 +3149,12 @@
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>3. Without saving, change the Allow Special Rate toggle on row B (a different row, not used by other tests).</t>
+          <t>6. Confirm the changed toggle state on row A is still present.</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Toggle state on row B changes. Save remains enabled.</t>
+          <t>Row A's toggle reflects the value saved in step 4.</t>
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
@@ -3210,35 +3172,77 @@
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>4. Click Save once.</t>
+          <t>7. Confirm the changed toggle state on row B is still present</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>The save completes. Save becomes disabled.</t>
+          <t>Row B's toggle reflects the value saved in step 4.</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOP-OPT-022</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Pending edit survives the row being scrolled out of view</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>discount-optimization</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>discount_optimization</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Grid has completed its first paint. Save is disabled</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>5. Reload the page and wait for the grid to complete its first paint.</t>
+          <t>1. Find the first available non-reserved row near the top of the grid and record its current toggle state.</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>The page reloads.</t>
+          <t>Row is identified by location name.</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
@@ -3256,12 +3260,12 @@
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>6. Confirm the changed toggle state on row A is still present.</t>
+          <t>2. Change the toggle on the target row.</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Row A's toggle reflects the value saved in step 4.</t>
+          <t>Toggle state changes; Save becomes enabled.</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
@@ -3279,77 +3283,35 @@
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>7. Confirm the changed toggle state on row B is still present</t>
+          <t>3. Scroll the grid container far enough down that the target row moves well off screen (hundreds of rows away).</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Row B's toggle reflects the value saved in step 4.</t>
+          <t>The target row is no longer visible and has been unloaded from the page — the grid keeps only a window of rows loaded at a time.</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>TC-DOP-OPT-023</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Pending edit survives the row being scrolled out of view</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>discount-optimization</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>discount_optimization</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>Grid has completed its first paint. Save is disabled</t>
-        </is>
-      </c>
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>1. Find the first available non-reserved row near the top of the grid and record its current toggle state.</t>
+          <t>4. Scroll back to the top of the grid.</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Row is identified by location name.</t>
+          <t>The target row reappears on the page, rebuilt from the saved state.</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
@@ -3367,12 +3329,12 @@
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2. Change the toggle on the target row.</t>
+          <t>5. Read the target row's toggle state again.</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Toggle state changes; Save becomes enabled.</t>
+          <t>The toggle still shows the changed value — the pending edit was not discarded by the re-render.</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
@@ -3390,12 +3352,12 @@
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>3. Scroll the grid container far enough down that the target row moves well off screen (hundreds of rows away).</t>
+          <t>6. Click Save and reload the page.</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>The target row is no longer visible and has been unloaded from the page — the grid keeps only a window of rows loaded at a time.</t>
+          <t>Save completes; the page reloads.</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
@@ -3413,35 +3375,77 @@
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>4. Scroll back to the top of the grid.</t>
+          <t>7. Confirm the changed toggle state persists after reload</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>The target row reappears on the page, rebuilt from the saved state.</t>
+          <t>Row shows the saved value.</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOP-OPT-023</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Add — opens the add affordance; Cancel discards cleanly</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>discount-optimization</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>discount_optimization</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Grid has completed its first paint</t>
+        </is>
+      </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>5. Read the target row's toggle state again.</t>
+          <t>1. Note the row count.</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>The toggle still shows the changed value — the pending edit was not discarded by the re-render.</t>
+          <t>Row count recorded.</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
@@ -3459,12 +3463,12 @@
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>6. Click Save and reload the page.</t>
+          <t>2. Click the Add button.</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Save completes; the page reloads.</t>
+          <t>The add affordance (dialog or inline form) opens.</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
@@ -3482,123 +3486,167 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>7. Confirm the changed toggle state persists after reload</t>
+          <t>3. Click Cancel without entering anything.</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Row shows the saved value.</t>
+          <t>The add affordance closes.</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>TC-DOP-OPT-024</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Add — opens the add affordance; Cancel discards cleanly</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>4. Confirm the row count is unchanged and Save is still disabled</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>No row was added; the grid is unchanged; Save is still disabled.</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOP-OPT-024</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Add button is present and visible on the Locations tab</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
         <is>
           <t>discount-optimization</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>discount_optimization</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>Grid has completed its first paint</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>1. Note the row count.</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>Row count recorded.</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr"/>
-      <c r="B89" t="inlineStr"/>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2. Click the Add button.</t>
+          <t>1. Look for the Add button in the Locations tab panel</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>The add affordance (dialog or inline form) opens.</t>
+          <t>The Add button is visible and enabled.</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr"/>
-      <c r="B90" t="inlineStr"/>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOP-OPT-025</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Switching tabs with no pending change does not show an unsaved-changes prompt (NM-3066)</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>discount-optimization</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>discount_optimization</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator
+Sample input 1: "Special Rate Exemptions by Service Type"
+Sample input 2: "Discount Optimization"</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>On the Discount Optimization Settings page, Locations tab active, no changes made. Grid has completed its first paint</t>
+        </is>
+      </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>3. Click Cancel without entering anything.</t>
+          <t>1. Confirm no change has been made (Save is disabled).</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>The add affordance closes.</t>
+          <t>Save is disabled.</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
@@ -3616,103 +3664,84 @@
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>4. Confirm the row count is unchanged and Save is still disabled</t>
+          <t>2. Click the "Special Rate Exemptions by Service Type" tab.</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>No row was added; the grid is unchanged; Save is still disabled.</t>
+          <t>The tab switches to tab 2 immediately.</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>TC-DOP-OPT-025</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Add button is present and visible on the Locations tab</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>3. Confirm no unsaved-changes dialog or prompt appeared.</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>No unsaved-changes prompt was shown — the switch was silent.</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>4. Click back to the "Discount Optimization" tab</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Tab 1 loads again.</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOP-OPT-026</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Switching from Tab 2 to Tab 1 with no pending change does not show an unsaved-changes prompt (NM-3066)</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
         <is>
           <t>discount-optimization</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>discount_optimization</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>Grid has completed its first paint</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>1. Look for the Add button in the Locations tab panel</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>The Add button is visible and enabled.</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>TC-DOP-OPT-026</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Switching tabs with no pending change does not show an unsaved-changes prompt (NM-3066)</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>discount-optimization</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>discount_optimization</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
@@ -3721,62 +3750,39 @@
 Sample input 2: "Discount Optimization"</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>On the Discount Optimization Settings page, Locations tab active, no changes made. Grid has completed its first paint</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="K94" t="inlineStr">
         <is>
           <t>1. Confirm no change has been made (Save is disabled).</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t>Save is disabled.</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr"/>
-      <c r="B94" t="inlineStr"/>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>2. Click the "Special Rate Exemptions by Service Type" tab.</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>The tab switches to tab 2 immediately.</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
@@ -3794,12 +3800,12 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>3. Confirm no unsaved-changes dialog or prompt appeared.</t>
+          <t>2. Click the "Special Rate Exemptions by Service Type" tab.</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>No unsaved-changes prompt was shown — the switch was silent.</t>
+          <t>Tab 2 loads with no prompt.</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
@@ -3817,102 +3823,103 @@
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>4. Click back to the "Discount Optimization" tab</t>
+          <t>3. Click back to the "Discount Optimization" tab.</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Tab 1 loads again.</t>
+          <t>Tab 1 loads immediately.</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>TC-DOP-OPT-027</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Switching from Tab 2 to Tab 1 with no pending change does not show an unsaved-changes prompt (NM-3066)</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>4. Confirm no unsaved-changes dialog or prompt appeared</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>No unsaved-changes prompt was shown — the switch was silent.</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOP-OPT-027</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Switching from Tab 1 to Tab 2 with an unsaved change shows the unsaved-changes prompt; Stay holds on Tab 1; Discard proceeds to Tab 2 (NM-3066)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
         <is>
           <t>discount-optimization</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>discount_optimization</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator
 Sample input 1: "Special Rate Exemptions by Service Type"
-Sample input 2: "Discount Optimization"</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
+Sample input 2: "Stay"
+Sample input 3: "Discard"</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>On the Discount Optimization Settings page, Locations tab active, no changes made. Grid has completed its first paint</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>1. Confirm no change has been made (Save is disabled).</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>On the Discount Optimization Settings page, Locations tab active. Grid has completed its first paint</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>1. Confirm Save is disabled.</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
         <is>
           <t>Save is disabled.</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr"/>
-      <c r="B98" t="inlineStr"/>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>2. Click the "Special Rate Exemptions by Service Type" tab.</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>Tab 2 loads with no prompt.</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
@@ -3930,12 +3937,12 @@
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>3. Click back to the "Discount Optimization" tab.</t>
+          <t>2. Toggle Allow Special Rate for a known row.</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Tab 1 loads immediately.</t>
+          <t>The row value changes and Save becomes enabled, confirming the edit is pending.</t>
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
@@ -3953,80 +3960,35 @@
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
-          <t>4. Confirm no unsaved-changes dialog or prompt appeared</t>
+          <t>3. Click the "Special Rate Exemptions by Service Type" tab.</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>No unsaved-changes prompt was shown — the switch was silent.</t>
+          <t>A confirmation dialog appears with title "Unsaved changes", body "Are you sure you want to leave this view? Any unsaved changes will be lost.", and buttons "Stay" and "Discard".</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>TC-DOP-OPT-028</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Switching from Tab 1 to Tab 2 with an unsaved change shows the unsaved-changes prompt; Stay holds on Tab 1; Discard proceeds to Tab 2 (NM-3066)</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>discount-optimization</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>discount_optimization</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator
-Sample input 1: "Special Rate Exemptions by Service Type"
-Sample input 2: "Stay"
-Sample input 3: "Discard"</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>On the Discount Optimization Settings page, Locations tab active. Grid has completed its first paint</t>
-        </is>
-      </c>
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>1. Confirm Save is disabled.</t>
+          <t>4. Click "Stay".</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Save is disabled.</t>
+          <t>The dialog closes; Tab 1 remains active; Save is still enabled, so the edit is still pending.</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
@@ -4044,12 +4006,12 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2. Toggle Allow Special Rate for a known row.</t>
+          <t>5. Click the "Special Rate Exemptions by Service Type" tab again.</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>The row value changes and Save becomes enabled, confirming the edit is pending.</t>
+          <t>The dialog appears again.</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
@@ -4067,35 +4029,80 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>3. Click the "Special Rate Exemptions by Service Type" tab.</t>
+          <t>6. Click "Discard"</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>A confirmation dialog appears with title "Unsaved changes", body "Are you sure you want to leave this view? Any unsaved changes will be lost.", and buttons "Stay" and "Discard".</t>
+          <t>The dialog closes; Tab 2 panel becomes visible; the unsaved change is dropped.</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
-      <c r="B104" t="inlineStr"/>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOP-OPT-028</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Switching from Tab 2 to Tab 1 with an unsaved change shows the unsaved-changes prompt; Stay holds on Tab 2; Discard proceeds to Tab 1 (NM-3066)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>discount-optimization</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>discount_optimization</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator
+Sample input 1: "Discount Optimization"
+Sample input 2: "Stay"
+Sample input 3: "Discard"</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>On the Discount Optimization Settings page, Tab 2 (Special Rate Exemptions by Service Type) active. Grid has completed its first paint</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>4. Click "Stay".</t>
+          <t>1. Switch to Tab</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>The dialog closes; Tab 1 remains active; Save is still enabled, so the edit is still pending.</t>
+          <t>Tab 2 renders with rows. Tab 2 Save is disabled.</t>
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
@@ -4113,12 +4120,12 @@
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>5. Click the "Special Rate Exemptions by Service Type" tab again.</t>
+          <t>2. 2. Toggle the Exempt checkbox for a known service type row.</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>The dialog appears again.</t>
+          <t>The checkbox value changes and Tab 2 Save becomes enabled, confirming the edit is pending.</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
@@ -4136,80 +4143,35 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>6. Click "Discard"</t>
+          <t>3. Click the "Discount Optimization" tab.</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>The dialog closes; Tab 2 panel becomes visible; the unsaved change is dropped.</t>
+          <t>A confirmation dialog appears with title "Unsaved changes", body "Are you sure you want to leave this view? Any unsaved changes will be lost.", and buttons "Stay" and "Discard".</t>
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>TC-DOP-OPT-029</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Switching from Tab 2 to Tab 1 with an unsaved change shows the unsaved-changes prompt; Stay holds on Tab 2; Discard proceeds to Tab 1 (NM-3066)</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>discount-optimization</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>discount_optimization</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator
-Sample input 1: "Discount Optimization"
-Sample input 2: "Stay"
-Sample input 3: "Discard"</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>On the Discount Optimization Settings page, Tab 2 (Special Rate Exemptions by Service Type) active. Grid has completed its first paint</t>
-        </is>
-      </c>
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>1. Switch to Tab</t>
+          <t>4. Click "Stay".</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Tab 2 renders with rows. Tab 2 Save is disabled.</t>
+          <t>The dialog closes; Tab 2 remains active; Tab 2 Save is still enabled, so the edit is still pending.</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
@@ -4227,12 +4189,12 @@
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2. 2. Toggle the Exempt checkbox for a known service type row.</t>
+          <t>5. Click the "Discount Optimization" tab again.</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>The checkbox value changes and Tab 2 Save becomes enabled, confirming the edit is pending.</t>
+          <t>The dialog appears again.</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
@@ -4250,35 +4212,77 @@
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>3. Click the "Discount Optimization" tab.</t>
+          <t>6. Click "Discard"</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>A confirmation dialog appears with title "Unsaved changes", body "Are you sure you want to leave this view? Any unsaved changes will be lost.", and buttons "Stay" and "Discard".</t>
+          <t>The dialog closes; Tab 1 panel becomes visible; the unsaved change is dropped.</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr"/>
-      <c r="B110" t="inlineStr"/>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOP-OPT-029</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Search includes deactivated locations by name and clears correctly (NM-3210)</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>discount-optimization</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>discount_optimization</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Grid has completed its first paint</t>
+        </is>
+      </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>4. Click "Stay".</t>
+          <t>1. Note the row count in the default view.</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>The dialog closes; Tab 2 remains active; Tab 2 Save is still enabled, so the edit is still pending.</t>
+          <t>Baseline row count recorded.</t>
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
@@ -4296,12 +4300,12 @@
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>5. Click the "Discount Optimization" tab again.</t>
+          <t>2. Apply an Active filter (if a filter control is present) to show only active locations.</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>The dialog appears again.</t>
+          <t>The grid shows a subset of rows corresponding to active locations.</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
@@ -4319,100 +4323,101 @@
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>6. Click "Discard"</t>
+          <t>3. Toggle to show inactive locations.</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>The dialog closes; Tab 1 panel becomes visible; the unsaved change is dropped.</t>
+          <t>The grid updates to show inactive locations. The row set differs from the active view.</t>
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>TC-DOP-OPT-030</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Search includes deactivated locations by name and clears correctly (NM-3210)</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>4. Toggle back to the default (all) view</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>The grid restores to the original baseline row count.</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOP-OPT-030</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Search returns deactivated locations (NM-3210 coverage)</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
         <is>
           <t>discount-optimization</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D114" t="inlineStr">
         <is>
           <t>discount_optimization</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E114" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
-Application: Navigator</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
+Application: Navigator
+Sample input 1: "Deactivat"</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="H114" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="I114" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr">
+      <c r="J114" t="inlineStr">
         <is>
           <t>Grid has completed its first paint</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>1. Note the row count in the default view.</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>Baseline row count recorded.</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr"/>
-      <c r="B114" t="inlineStr"/>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2. Apply an Active filter (if a filter control is present) to show only active locations.</t>
+          <t>1. Type a fragment of a known deactivated location name into the search box (e.g. "Deactivat").</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>The grid shows a subset of rows corresponding to active locations.</t>
+          <t>The grid filters and shows rows whose name contains "Deactivat".</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
@@ -4430,101 +4435,100 @@
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>3. Toggle to show inactive locations.</t>
+          <t>2. Confirm at least one deactivated row appears</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>The grid updates to show inactive locations. The row set differs from the active view.</t>
+          <t>One or more rows with a deactivated location name are shown — deactivated locations are included, not silently excluded.</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr"/>
-      <c r="B116" t="inlineStr"/>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>4. Toggle back to the default (all) view</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>The grid restores to the original baseline row count.</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>TC-DOP-OPT-031</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Search returns deactivated locations (NM-3210 coverage)</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOP-OPT-031</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Allow Special Rate toggle enables Save — NM-2917 regression lock</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
         <is>
           <t>discount-optimization</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D116" t="inlineStr">
         <is>
           <t>discount_optimization</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="E116" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
-Application: Navigator
-Sample input 1: "Deactivat"</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
+Application: Navigator</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="H116" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="I116" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>Grid has completed its first paint</t>
-        </is>
-      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Grid has completed its first paint. Save is disabled</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>1. Confirm Save is disabled.</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Save button is disabled.</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>1. Type a fragment of a known deactivated location name into the search box (e.g. "Deactivat").</t>
+          <t>2. Click the Allow Special Rate toggle button on any row.</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>The grid filters and shows rows whose name contains "Deactivat".</t>
+          <t>The toggle state changes.</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
@@ -4542,12 +4546,12 @@
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2. Confirm at least one deactivated row appears</t>
+          <t>3. Read the Save button state</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>One or more rows with a deactivated location name are shown — deactivated locations are included, not silently excluded.</t>
+          <t>Save is now enabled.</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
@@ -4555,12 +4559,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>TC-DOP-OPT-032</t>
+          <t xml:space="preserve">TC-DOP-OPT-032</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Allow Special Rate toggle enables Save — NM-2917 regression lock</t>
+          <t>Rejected save surfaces the failure and keeps the change pending</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4607,12 +4611,12 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>1. Confirm Save is disabled.</t>
+          <t>1. Configure the test so that any save attempt on the optimization endpoint returns a server error, while leaving normal page data loading unaffected.</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Save button is disabled.</t>
+          <t>The interception is active; page data loads as normal.</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
@@ -4630,12 +4634,12 @@
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>2. Click the Allow Special Rate toggle button on any row.</t>
+          <t>2. Change the Allow Special Rate toggle on a row.</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>The toggle state changes.</t>
+          <t>Toggle state changes; Save becomes enabled.</t>
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
@@ -4653,77 +4657,35 @@
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>3. Read the Save button state</t>
+          <t>3. Click Save.</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Save is now enabled.</t>
+          <t>The save request is sent; the route intercepts it and returns 500. The request never reaches the server.</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>TC-DOP-OPT-033</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Rejected save surfaces the failure and keeps the change pending</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>discount-optimization</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>discount_optimization</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>Grid has completed its first paint. Save is disabled</t>
-        </is>
-      </c>
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>1. Configure the test so that any save attempt on the optimization endpoint returns a server error, while leaving normal page data loading unaffected.</t>
+          <t>4. Confirm the route interception fired.</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>The interception is active; page data loads as normal.</t>
+          <t>The interceptor was called — proving the request was stopped before the server.</t>
         </is>
       </c>
       <c r="M122" t="inlineStr"/>
@@ -4741,35 +4703,78 @@
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>2. Change the Allow Special Rate toggle on a row.</t>
+          <t>5. Assert the app does not behave as if the save succeeded</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Toggle state changes; Save becomes enabled.</t>
+          <t>At least one of: an error element is visible, Save is still enabled, or the changed value is still present in the UI.</t>
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr"/>
-      <c r="B124" t="inlineStr"/>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
+      <c r="A124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOP-OPT-033</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Cancelling an incomplete Add leaves Save disabled</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>discount-optimization</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>discount_optimization</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator
+Sample input 1: "Select a Location"</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Grid has completed its first paint. Save is disabled</t>
+        </is>
+      </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>3. Click Save.</t>
+          <t>1. Confirm Save is disabled on a fresh load.</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>The save request is sent; the route intercepts it and returns 500. The request never reaches the server.</t>
+          <t>Save is disabled.</t>
         </is>
       </c>
       <c r="M124" t="inlineStr"/>
@@ -4787,12 +4792,12 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>4. Confirm the route interception fired.</t>
+          <t>2. Click the Add button.</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>The interceptor was called — proving the request was stopped before the server.</t>
+          <t>The Add panel opens with Update and Cancel buttons.</t>
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
@@ -4810,78 +4815,35 @@
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>5. Assert the app does not behave as if the save succeeded</t>
+          <t>3. Click "Select a Location" to open the location picker.</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>At least one of: an error element is visible, Save is still enabled, or the changed value is still present in the UI.</t>
+          <t>The "Change Local Office" picker dialog appears with a search input.</t>
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>TC-DOP-OPT-034</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Cancelling an incomplete Add leaves Save disabled</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>discount-optimization</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>discount_optimization</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator
-Sample input 1: "Select a Location"</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>Grid has completed its first paint. Save is disabled</t>
-        </is>
-      </c>
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>1. Confirm Save is disabled on a fresh load.</t>
+          <t>4. Cancel the picker dialog without selecting anything.</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>Save is disabled.</t>
+          <t>The picker closes.</t>
         </is>
       </c>
       <c r="M127" t="inlineStr"/>
@@ -4899,12 +4861,12 @@
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2. Click the Add button.</t>
+          <t>5. Cancel the Add panel.</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>The Add panel opens with Update and Cancel buttons.</t>
+          <t>The Add panel closes.</t>
         </is>
       </c>
       <c r="M128" t="inlineStr"/>
@@ -4922,35 +4884,77 @@
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>3. Click "Select a Location" to open the location picker.</t>
+          <t>6. Read the Save button state</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>The "Change Local Office" picker dialog appears with a search input.</t>
+          <t>Save is still disabled — the form has no unsaved changes pending.</t>
         </is>
       </c>
       <c r="M129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr"/>
-      <c r="B130" t="inlineStr"/>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
+      <c r="A130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOP-OPT-034</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Save round-trip — a Special Rate Start Date change persists after reload</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>discount-optimization</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>discount_optimization</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Grid has completed its first paint</t>
+        </is>
+      </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>4. Cancel the picker dialog without selecting anything.</t>
+          <t>1. Confirm Save is disabled on a fresh pristine load.</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>The picker closes.</t>
+          <t>Save is disabled.</t>
         </is>
       </c>
       <c r="M130" t="inlineStr"/>
@@ -4968,12 +4972,12 @@
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>5. Cancel the Add panel.</t>
+          <t>2. Open the calendar picker for a known row (InterContinental Chicago) and select a date one month ahead.</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>The Add panel closes.</t>
+          <t>The calendar popover closes and the date input shows the selected date. Save becomes enabled.</t>
         </is>
       </c>
       <c r="M131" t="inlineStr"/>
@@ -4991,77 +4995,35 @@
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>6. Read the Save button state</t>
+          <t>3. Click Save.</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>Save is still disabled — the form has no unsaved changes pending.</t>
+          <t>Save is submitted successfully and Save becomes disabled.</t>
         </is>
       </c>
       <c r="M132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>TC-DOP-OPT-035</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Save round-trip — a Special Rate Start Date change persists after reload</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>discount-optimization</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>discount_optimization</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>Grid has completed its first paint</t>
-        </is>
-      </c>
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>1. Confirm Save is disabled on a fresh pristine load.</t>
+          <t>4. Reload the page and wait for the grid to complete its first paint.</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Save is disabled.</t>
+          <t>The page reloads.</t>
         </is>
       </c>
       <c r="M133" t="inlineStr"/>
@@ -5079,116 +5041,47 @@
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2. Open the calendar picker for a known row (InterContinental Chicago) and select a date one month ahead.</t>
+          <t>5. Confirm the saved date is still shown on the same row</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>The calendar popover closes and the date input shows the selected date. Save becomes enabled.</t>
+          <t>The date persists after reload. The change was not lost.</t>
         </is>
       </c>
       <c r="M134" t="inlineStr"/>
     </row>
-    <row r="135">
-      <c r="A135" t="inlineStr"/>
-      <c r="B135" t="inlineStr"/>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>3. Click Save.</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>Save is submitted successfully and Save becomes disabled.</t>
-        </is>
-      </c>
-      <c r="M135" t="inlineStr"/>
-    </row>
+    <row r="135"/>
     <row r="136">
-      <c r="A136" t="inlineStr"/>
-      <c r="B136" t="inlineStr"/>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>4. Reload the page and wait for the grid to complete its first paint.</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>The page reloads.</t>
-        </is>
-      </c>
-      <c r="M136" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr"/>
-      <c r="B137" t="inlineStr"/>
-      <c r="C137" t="inlineStr"/>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>5. Confirm the saved date is still shown on the same row</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>The date persists after reload. The change was not lost.</t>
-        </is>
-      </c>
-      <c r="M137" t="inlineStr"/>
-    </row>
-    <row r="138"/>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>SUMMARY</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>Discount Optimization — Locations</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr"/>
-      <c r="D139" s="2" t="inlineStr"/>
-      <c r="E139" s="2" t="inlineStr"/>
-      <c r="F139" s="2" t="inlineStr"/>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>Automated: 34 / Pending: 1</t>
-        </is>
-      </c>
-      <c r="I139" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr"/>
+      <c r="D136" s="2" t="inlineStr"/>
+      <c r="E136" s="2" t="inlineStr"/>
+      <c r="F136" s="2" t="inlineStr"/>
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automated: 34 / Pending: 0</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
         <is>
           <t>Pass:34 Fail:0 Skipped:0 Blocked:0</t>
         </is>
       </c>
-      <c r="J139" s="2" t="inlineStr"/>
-      <c r="K139" s="2" t="inlineStr"/>
-      <c r="L139" s="2" t="inlineStr"/>
-      <c r="M139" s="2" t="inlineStr">
+      <c r="J136" s="2" t="inlineStr"/>
+      <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr"/>
+      <c r="M136" s="2" t="inlineStr">
         <is>
           <t>Last Updated: 2026-08-17</t>
         </is>
